--- a/kamerton-finmodel.xlsx
+++ b/kamerton-finmodel.xlsx
@@ -240,7 +240,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Налог считается за календарный год, как по закону: 15% от годовой прибыли за вычетом убытков прошлых лет или минимальный налог 1% от годовой выручки — что больше. Месяц 0 (разработка MVP) входит в 1-й год.</t>
+          <t xml:space="preserve">УСН «доходы минус расходы», 15%. Налог считается за год целиком: 15% с годовой прибыли за вычетом непогашенных убытков прошлых лет, но не меньше минимального налога 1% от годовой выручки (НК РФ, ст. 346.18). Годовая сумма распределена поровну на 12 месяцев года, как начисление: так месячная прибыль не проваливается в последний месяц года, а годовой налог тот же. Платится авансами по кварталам</t>
         </r>
       </text>
     </comment>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">Прибыль до налога нарастающим итогом (для переноса убытков)</t>
   </si>
   <si>
-    <t xml:space="preserve">Налог УСН за год (начисляется в последний месяц года)</t>
+    <t xml:space="preserve">Налог УСН (годовой налог, распределён поровну по месяцам года)</t>
   </si>
   <si>
     <t xml:space="preserve">Расходы с налогом, итого</t>
@@ -2898,112 +2898,112 @@
                   <c:v>-3085641</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-512416.279569472</c:v>
+                  <c:v>-516655.792666293</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-527577.651039087</c:v>
+                  <c:v>-531817.164135908</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-539457.672066428</c:v>
+                  <c:v>-543697.185163248</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-448701.434156205</c:v>
+                  <c:v>-452940.947253026</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-372103.187884491</c:v>
+                  <c:v>-376342.700981311</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-295754.100832566</c:v>
+                  <c:v>-299993.613929386</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-219889.307972</c:v>
+                  <c:v>-224128.821068821</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-144845.390229076</c:v>
+                  <c:v>-149084.903325896</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-70962.4621551324</c:v>
+                  <c:v>-75201.9752519532</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1471.6314082389</c:v>
+                  <c:v>-2767.88168858185</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>72230.3543005119</c:v>
+                  <c:v>67990.8412036911</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>83550.8676471105</c:v>
+                  <c:v>130185.511712139</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>194894.137570647</c:v>
+                  <c:v>181555.37699082</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>255582.137181753</c:v>
+                  <c:v>242243.376601926</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>316602.555767722</c:v>
+                  <c:v>303263.795187895</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>378048.517833088</c:v>
+                  <c:v>364709.757253261</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>439971.373979824</c:v>
+                  <c:v>426632.613399997</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>502393.435270255</c:v>
+                  <c:v>489054.674690428</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>565316.379678377</c:v>
+                  <c:v>551977.61909855</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>628727.466406865</c:v>
+                  <c:v>615388.705827038</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>692604.137859233</c:v>
+                  <c:v>679265.377279406</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>756917.432654953</c:v>
+                  <c:v>743578.672075126</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>821634.508810944</c:v>
+                  <c:v>808295.748231116</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>726655.367509523</c:v>
+                  <c:v>873381.73388762</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>868674.481546596</c:v>
+                  <c:v>686601.850538887</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>930811.98842722</c:v>
+                  <c:v>748739.357419512</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>993198.896262073</c:v>
+                  <c:v>811126.265254365</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1055803.87553065</c:v>
+                  <c:v>873731.244522941</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1118597.13582209</c:v>
+                  <c:v>936524.50481438</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1181550.55419264</c:v>
+                  <c:v>999477.923184935</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1244637.71831081</c:v>
+                  <c:v>1062565.0873031</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1307833.90911795</c:v>
+                  <c:v>1125761.27811024</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1371116.04203485</c:v>
+                  <c:v>1189043.41102715</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1434462.58122373</c:v>
+                  <c:v>1252389.95021602</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1497853.43783211</c:v>
+                  <c:v>1315780.8068244</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-623601.711776527</c:v>
+                  <c:v>1379197.22930827</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3018,11 +3018,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="53315789"/>
-        <c:axId val="59093022"/>
+        <c:axId val="32951324"/>
+        <c:axId val="91744264"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="53315789"/>
+        <c:axId val="32951324"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3088,7 +3088,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59093022"/>
+        <c:crossAx val="91744264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3096,7 +3096,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59093022"/>
+        <c:axId val="91744264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3169,7 +3169,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53315789"/>
+        <c:crossAx val="32951324"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3297,109 +3297,109 @@
                   <c:v>-3085641</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3598057.27956947</c:v>
+                  <c:v>-3602296.79266629</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-4125634.93060856</c:v>
+                  <c:v>-4134113.9568022</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4665092.60267499</c:v>
+                  <c:v>-4677811.14196545</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-5113794.03683119</c:v>
+                  <c:v>-5130752.08921847</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-5485897.22471568</c:v>
+                  <c:v>-5507094.79019979</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-5781651.32554825</c:v>
+                  <c:v>-5807088.40412917</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-6001540.63352025</c:v>
+                  <c:v>-6031217.22519799</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-6146386.02374932</c:v>
+                  <c:v>-6180302.12852389</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-6217348.48590446</c:v>
+                  <c:v>-6255504.10377584</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-6215876.85449622</c:v>
+                  <c:v>-6258271.98546443</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-6143646.5001957</c:v>
+                  <c:v>-6190281.14426073</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-6060095.63254859</c:v>
+                  <c:v>-6060095.6325486</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-5865201.49497795</c:v>
+                  <c:v>-5878540.25555778</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-5609619.35779619</c:v>
+                  <c:v>-5636296.87895585</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-5293016.80202847</c:v>
+                  <c:v>-5333033.08376795</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-4914968.28419538</c:v>
+                  <c:v>-4968323.32651469</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-4474996.91021556</c:v>
+                  <c:v>-4541690.7131147</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-3972603.4749453</c:v>
+                  <c:v>-4052636.03842427</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-3407287.09526693</c:v>
+                  <c:v>-3500658.41932572</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2778559.62886006</c:v>
+                  <c:v>-2885269.71349868</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-2085955.49100083</c:v>
+                  <c:v>-2206004.33621927</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-1329038.05834588</c:v>
+                  <c:v>-1462425.66414415</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-507403.549534932</c:v>
+                  <c:v>-654129.91591303</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>219251.817974591</c:v>
+                  <c:v>219251.81797459</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1087926.29952119</c:v>
+                  <c:v>905853.668513477</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2018738.28794841</c:v>
+                  <c:v>1654593.02593299</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3011937.18421048</c:v>
+                  <c:v>2465719.29118735</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4067741.05974113</c:v>
+                  <c:v>3339450.53571029</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5186338.19556322</c:v>
+                  <c:v>4275975.04052468</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>6367888.74975586</c:v>
+                  <c:v>5275452.96370961</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7612526.46806667</c:v>
+                  <c:v>6338018.05101271</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8920360.37718462</c:v>
+                  <c:v>7463779.32912295</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10291476.4192195</c:v>
+                  <c:v>8652822.74015009</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>11725939.0004432</c:v>
+                  <c:v>9905212.69036611</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>13223792.4382753</c:v>
+                  <c:v>11220993.4971905</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>12600190.7264988</c:v>
@@ -3417,11 +3417,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="43424367"/>
-        <c:axId val="31674857"/>
+        <c:axId val="62100803"/>
+        <c:axId val="2820489"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="43424367"/>
+        <c:axId val="62100803"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3487,7 +3487,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31674857"/>
+        <c:crossAx val="2820489"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3495,7 +3495,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31674857"/>
+        <c:axId val="2820489"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3568,7 +3568,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43424367"/>
+        <c:crossAx val="62100803"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3816,11 +3816,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="52233278"/>
-        <c:axId val="83190625"/>
+        <c:axId val="54885058"/>
+        <c:axId val="21304459"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52233278"/>
+        <c:axId val="54885058"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3886,7 +3886,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83190625"/>
+        <c:crossAx val="21304459"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3894,7 +3894,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83190625"/>
+        <c:axId val="21304459"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3967,7 +3967,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52233278"/>
+        <c:crossAx val="54885058"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4215,11 +4215,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="71298979"/>
-        <c:axId val="33229119"/>
+        <c:axId val="98428398"/>
+        <c:axId val="36550391"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="71298979"/>
+        <c:axId val="98428398"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4285,7 +4285,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33229119"/>
+        <c:crossAx val="36550391"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4293,7 +4293,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33229119"/>
+        <c:axId val="36550391"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4366,7 +4366,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71298979"/>
+        <c:crossAx val="98428398"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4405,9 +4405,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>471240</xdr:colOff>
+      <xdr:colOff>470520</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>136080</xdr:rowOff>
+      <xdr:rowOff>135360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4416,7 +4416,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4781520" y="12001680"/>
-        <a:ext cx="6473880" cy="3841200"/>
+        <a:ext cx="6473160" cy="3840480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4435,9 +4435,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>471240</xdr:colOff>
+      <xdr:colOff>470520</xdr:colOff>
       <xdr:row>108</xdr:row>
-      <xdr:rowOff>136440</xdr:rowOff>
+      <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4446,7 +4446,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4781520" y="16164000"/>
-        <a:ext cx="6473880" cy="3841560"/>
+        <a:ext cx="6473160" cy="3840840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4465,9 +4465,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>471240</xdr:colOff>
+      <xdr:colOff>470520</xdr:colOff>
       <xdr:row>131</xdr:row>
-      <xdr:rowOff>136080</xdr:rowOff>
+      <xdr:rowOff>135360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4476,7 +4476,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4781520" y="20326680"/>
-        <a:ext cx="6473880" cy="3840840"/>
+        <a:ext cx="6473160" cy="3840120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4495,9 +4495,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>471240</xdr:colOff>
+      <xdr:colOff>470520</xdr:colOff>
       <xdr:row>154</xdr:row>
-      <xdr:rowOff>136080</xdr:rowOff>
+      <xdr:rowOff>135360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4506,7 +4506,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4781520" y="24489000"/>
-        <a:ext cx="6473880" cy="3841200"/>
+        <a:ext cx="6473160" cy="3840480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C25" s="6" t="n">
         <f aca="false">SUM('3 года подробно'!O40:Z40)</f>
-        <v>6279347.45052319</v>
+        <v>6279347.45052318</v>
       </c>
       <c r="D25" s="6" t="n">
         <f aca="false">SUM('3 года подробно'!AA40:AL40)</f>
@@ -5167,11 +5167,11 @@
       </c>
       <c r="B27" s="6" t="n">
         <f aca="false">'3 года подробно'!N41</f>
-        <v>-6060095.63254859</v>
+        <v>-6060095.6325486</v>
       </c>
       <c r="C27" s="6" t="n">
         <f aca="false">'3 года подробно'!Z41</f>
-        <v>219251.817974591</v>
+        <v>219251.81797459</v>
       </c>
       <c r="D27" s="6" t="n">
         <f aca="false">'3 года подробно'!AL41</f>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">IFERROR(SUM(B25:C25)/SUM(B18:C21),0)</f>
-        <v>0.010610462893841</v>
+        <v>0.0106104628938409</v>
       </c>
       <c r="D28" s="10" t="n">
         <f aca="false">IFERROR(SUM(B25:D25)/SUM(B18:D21),0)</f>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="B29" s="6" t="n">
         <f aca="false">-MIN(0,MIN('3 года подробно'!B41:AL41))</f>
-        <v>6217348.48590446</v>
+        <v>6258271.98546443</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>48</v>
@@ -10512,148 +10512,148 @@
         <v>0</v>
       </c>
       <c r="C37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="D37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="E37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="F37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="G37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="H37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="I37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="J37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="K37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="L37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="M37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="N37" s="9" t="n">
-        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,N36))</f>
-        <v>50874.157161849</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($B$26:$N$26),Вводные!$B$27*MAX(0,$N$36))/12</f>
+        <v>4239.51309682075</v>
       </c>
       <c r="O37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="P37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="R37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="S37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="T37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="U37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="V37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="W37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="X37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="Y37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="Z37" s="9" t="n">
-        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,Z36)-MAX(0,N36)))</f>
-        <v>160065.126957924</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($O$26:$Z$26),Вводные!$B$27*(MAX(0,$Z$36)-MAX(0,$N$36)))/12</f>
+        <v>13338.760579827</v>
       </c>
       <c r="AA37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AB37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AC37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AD37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AE37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AF37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AG37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AH37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AI37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AJ37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AK37" s="9" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
       <c r="AL37" s="9" t="n">
-        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,AL36)-MAX(0,Z36)))</f>
-        <v>2184871.5720925</v>
+        <f aca="false">MAX(Вводные!$B$28*SUM($AA$26:$AL$26),Вводные!$B$27*(MAX(0,$AL$36)-MAX(0,$Z$36)))/12</f>
+        <v>182072.631007709</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10666,147 +10666,147 @@
       </c>
       <c r="C38" s="9" t="n">
         <f aca="false">C33+C37</f>
-        <v>535893.521233048</v>
+        <v>540133.034329869</v>
       </c>
       <c r="D38" s="9" t="n">
         <f aca="false">D33+D37</f>
-        <v>598536.193100186</v>
+        <v>602775.706197007</v>
       </c>
       <c r="E38" s="9" t="n">
         <f aca="false">E33+E37</f>
-        <v>660750.857385542</v>
+        <v>664990.370482362</v>
       </c>
       <c r="F38" s="9" t="n">
         <f aca="false">F33+F37</f>
-        <v>667439.959735743</v>
+        <v>671679.472832564</v>
       </c>
       <c r="G38" s="9" t="n">
         <f aca="false">G33+G37</f>
-        <v>673720.449698867</v>
+        <v>677959.962795688</v>
       </c>
       <c r="H38" s="9" t="n">
         <f aca="false">H33+H37</f>
-        <v>679628.289533753</v>
+        <v>683867.802630574</v>
       </c>
       <c r="I38" s="9" t="n">
         <f aca="false">I33+I37</f>
-        <v>685281.246003525</v>
+        <v>689520.759100345</v>
       </c>
       <c r="J38" s="9" t="n">
         <f aca="false">J33+J37</f>
-        <v>690695.953312053</v>
+        <v>694935.466408873</v>
       </c>
       <c r="K38" s="9" t="n">
         <f aca="false">K33+K37</f>
-        <v>695877.821531988</v>
+        <v>700117.334628809</v>
       </c>
       <c r="L38" s="9" t="n">
         <f aca="false">L33+L37</f>
-        <v>700830.267362308</v>
+        <v>705069.780459129</v>
       </c>
       <c r="M38" s="9" t="n">
         <f aca="false">M33+M37</f>
-        <v>705557.447437884</v>
+        <v>709796.960534705</v>
       </c>
       <c r="N38" s="9" t="n">
         <f aca="false">N33+N37</f>
-        <v>767658.342398593</v>
+        <v>721023.698333564</v>
       </c>
       <c r="O38" s="9" t="n">
         <f aca="false">O33+O37</f>
-        <v>729255.728307091</v>
+        <v>742594.488886918</v>
       </c>
       <c r="P38" s="9" t="n">
         <f aca="false">P33+P37</f>
-        <v>741586.631025746</v>
+        <v>754925.391605573</v>
       </c>
       <c r="Q38" s="9" t="n">
         <f aca="false">Q33+Q37</f>
-        <v>753868.143027059</v>
+        <v>767206.903606886</v>
       </c>
       <c r="R38" s="9" t="n">
         <f aca="false">R33+R37</f>
-        <v>766142.478081302</v>
+        <v>779481.238661129</v>
       </c>
       <c r="S38" s="9" t="n">
         <f aca="false">S33+S37</f>
-        <v>778438.734592063</v>
+        <v>791777.49517189</v>
       </c>
       <c r="T38" s="9" t="n">
         <f aca="false">T33+T37</f>
-        <v>790776.085173265</v>
+        <v>804114.845753092</v>
       </c>
       <c r="U38" s="9" t="n">
         <f aca="false">U33+U37</f>
-        <v>803166.627476624</v>
+        <v>816505.388056451</v>
       </c>
       <c r="V38" s="9" t="n">
         <f aca="false">V33+V37</f>
-        <v>815617.373139067</v>
+        <v>828956.133718894</v>
       </c>
       <c r="W38" s="9" t="n">
         <f aca="false">W33+W37</f>
-        <v>828131.673959426</v>
+        <v>841470.434539253</v>
       </c>
       <c r="X38" s="9" t="n">
         <f aca="false">X33+X37</f>
-        <v>840710.257070223</v>
+        <v>854049.01765005</v>
       </c>
       <c r="Y38" s="9" t="n">
         <f aca="false">Y33+Y37</f>
-        <v>853351.982941733</v>
+        <v>866690.74352156</v>
       </c>
       <c r="Z38" s="9" t="n">
         <f aca="false">Z33+Z37</f>
-        <v>1026119.53047559</v>
+        <v>879393.164097489</v>
       </c>
       <c r="AA38" s="9" t="n">
         <f aca="false">AA33+AA37</f>
-        <v>875091.234478654</v>
+        <v>1057163.86548636</v>
       </c>
       <c r="AB38" s="9" t="n">
         <f aca="false">AB33+AB37</f>
-        <v>887744.739864557</v>
+        <v>1069817.37087227</v>
       </c>
       <c r="AC38" s="9" t="n">
         <f aca="false">AC33+AC37</f>
-        <v>900446.717715708</v>
+        <v>1082519.34872342</v>
       </c>
       <c r="AD38" s="9" t="n">
         <f aca="false">AD33+AD37</f>
-        <v>913192.735129977</v>
+        <v>1095265.36613769</v>
       </c>
       <c r="AE38" s="9" t="n">
         <f aca="false">AE33+AE37</f>
-        <v>925978.270883232</v>
+        <v>1108050.90189094</v>
       </c>
       <c r="AF38" s="9" t="n">
         <f aca="false">AF33+AF37</f>
-        <v>938798.800240188</v>
+        <v>1120871.4312479</v>
       </c>
       <c r="AG38" s="9" t="n">
         <f aca="false">AG33+AG37</f>
-        <v>951649.854695111</v>
+        <v>1133722.48570282</v>
       </c>
       <c r="AH38" s="9" t="n">
         <f aca="false">AH33+AH37</f>
-        <v>964527.062970003</v>
+        <v>1146599.69397771</v>
       </c>
       <c r="AI38" s="9" t="n">
         <f aca="false">AI33+AI37</f>
-        <v>977426.178070678</v>
+        <v>1159498.80907839</v>
       </c>
       <c r="AJ38" s="9" t="n">
         <f aca="false">AJ33+AJ37</f>
-        <v>990343.094047044</v>
+        <v>1172415.72505475</v>
       </c>
       <c r="AK38" s="9" t="n">
         <f aca="false">AK33+AK37</f>
-        <v>1003273.85522642</v>
+        <v>1185346.48623413</v>
       </c>
       <c r="AL38" s="9" t="n">
         <f aca="false">AL33+AL37</f>
-        <v>3201086.23211095</v>
+        <v>1198287.29102615</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10819,147 +10819,147 @@
       </c>
       <c r="C40" s="6" t="n">
         <f aca="false">C35-C37</f>
-        <v>-512416.279569472</v>
+        <v>-516655.792666293</v>
       </c>
       <c r="D40" s="6" t="n">
         <f aca="false">D35-D37</f>
-        <v>-527577.651039087</v>
+        <v>-531817.164135908</v>
       </c>
       <c r="E40" s="6" t="n">
         <f aca="false">E35-E37</f>
-        <v>-539457.672066428</v>
+        <v>-543697.185163248</v>
       </c>
       <c r="F40" s="6" t="n">
         <f aca="false">F35-F37</f>
-        <v>-448701.434156205</v>
+        <v>-452940.947253026</v>
       </c>
       <c r="G40" s="6" t="n">
         <f aca="false">G35-G37</f>
-        <v>-372103.187884491</v>
+        <v>-376342.700981311</v>
       </c>
       <c r="H40" s="6" t="n">
         <f aca="false">H35-H37</f>
-        <v>-295754.100832566</v>
+        <v>-299993.613929386</v>
       </c>
       <c r="I40" s="6" t="n">
         <f aca="false">I35-I37</f>
-        <v>-219889.307972</v>
+        <v>-224128.821068821</v>
       </c>
       <c r="J40" s="6" t="n">
         <f aca="false">J35-J37</f>
-        <v>-144845.390229076</v>
+        <v>-149084.903325896</v>
       </c>
       <c r="K40" s="6" t="n">
         <f aca="false">K35-K37</f>
-        <v>-70962.4621551324</v>
+        <v>-75201.9752519532</v>
       </c>
       <c r="L40" s="6" t="n">
         <f aca="false">L35-L37</f>
-        <v>1471.6314082389</v>
+        <v>-2767.88168858185</v>
       </c>
       <c r="M40" s="6" t="n">
         <f aca="false">M35-M37</f>
-        <v>72230.3543005119</v>
+        <v>67990.8412036911</v>
       </c>
       <c r="N40" s="6" t="n">
         <f aca="false">N35-N37</f>
-        <v>83550.8676471105</v>
+        <v>130185.511712139</v>
       </c>
       <c r="O40" s="6" t="n">
         <f aca="false">O35-O37</f>
-        <v>194894.137570647</v>
+        <v>181555.37699082</v>
       </c>
       <c r="P40" s="6" t="n">
         <f aca="false">P35-P37</f>
-        <v>255582.137181753</v>
+        <v>242243.376601926</v>
       </c>
       <c r="Q40" s="6" t="n">
         <f aca="false">Q35-Q37</f>
-        <v>316602.555767722</v>
+        <v>303263.795187895</v>
       </c>
       <c r="R40" s="6" t="n">
         <f aca="false">R35-R37</f>
-        <v>378048.517833088</v>
+        <v>364709.757253261</v>
       </c>
       <c r="S40" s="6" t="n">
         <f aca="false">S35-S37</f>
-        <v>439971.373979824</v>
+        <v>426632.613399997</v>
       </c>
       <c r="T40" s="6" t="n">
         <f aca="false">T35-T37</f>
-        <v>502393.435270255</v>
+        <v>489054.674690428</v>
       </c>
       <c r="U40" s="6" t="n">
         <f aca="false">U35-U37</f>
-        <v>565316.379678377</v>
+        <v>551977.61909855</v>
       </c>
       <c r="V40" s="6" t="n">
         <f aca="false">V35-V37</f>
-        <v>628727.466406865</v>
+        <v>615388.705827038</v>
       </c>
       <c r="W40" s="6" t="n">
         <f aca="false">W35-W37</f>
-        <v>692604.137859233</v>
+        <v>679265.377279406</v>
       </c>
       <c r="X40" s="6" t="n">
         <f aca="false">X35-X37</f>
-        <v>756917.432654953</v>
+        <v>743578.672075126</v>
       </c>
       <c r="Y40" s="6" t="n">
         <f aca="false">Y35-Y37</f>
-        <v>821634.508810944</v>
+        <v>808295.748231116</v>
       </c>
       <c r="Z40" s="6" t="n">
         <f aca="false">Z35-Z37</f>
-        <v>726655.367509523</v>
+        <v>873381.73388762</v>
       </c>
       <c r="AA40" s="6" t="n">
         <f aca="false">AA35-AA37</f>
-        <v>868674.481546596</v>
+        <v>686601.850538887</v>
       </c>
       <c r="AB40" s="6" t="n">
         <f aca="false">AB35-AB37</f>
-        <v>930811.98842722</v>
+        <v>748739.357419512</v>
       </c>
       <c r="AC40" s="6" t="n">
         <f aca="false">AC35-AC37</f>
-        <v>993198.896262073</v>
+        <v>811126.265254365</v>
       </c>
       <c r="AD40" s="6" t="n">
         <f aca="false">AD35-AD37</f>
-        <v>1055803.87553065</v>
+        <v>873731.244522941</v>
       </c>
       <c r="AE40" s="6" t="n">
         <f aca="false">AE35-AE37</f>
-        <v>1118597.13582209</v>
+        <v>936524.50481438</v>
       </c>
       <c r="AF40" s="6" t="n">
         <f aca="false">AF35-AF37</f>
-        <v>1181550.55419264</v>
+        <v>999477.923184935</v>
       </c>
       <c r="AG40" s="6" t="n">
         <f aca="false">AG35-AG37</f>
-        <v>1244637.71831081</v>
+        <v>1062565.0873031</v>
       </c>
       <c r="AH40" s="6" t="n">
         <f aca="false">AH35-AH37</f>
-        <v>1307833.90911795</v>
+        <v>1125761.27811024</v>
       </c>
       <c r="AI40" s="6" t="n">
         <f aca="false">AI35-AI37</f>
-        <v>1371116.04203485</v>
+        <v>1189043.41102715</v>
       </c>
       <c r="AJ40" s="6" t="n">
         <f aca="false">AJ35-AJ37</f>
-        <v>1434462.58122373</v>
+        <v>1252389.95021602</v>
       </c>
       <c r="AK40" s="6" t="n">
         <f aca="false">AK35-AK37</f>
-        <v>1497853.43783211</v>
+        <v>1315780.8068244</v>
       </c>
       <c r="AL40" s="6" t="n">
         <f aca="false">AL35-AL37</f>
-        <v>-623601.711776527</v>
+        <v>1379197.22930827</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10972,143 +10972,143 @@
       </c>
       <c r="C41" s="6" t="n">
         <f aca="false">B41+C40</f>
-        <v>-3598057.27956947</v>
+        <v>-3602296.79266629</v>
       </c>
       <c r="D41" s="6" t="n">
         <f aca="false">C41+D40</f>
-        <v>-4125634.93060856</v>
+        <v>-4134113.9568022</v>
       </c>
       <c r="E41" s="6" t="n">
         <f aca="false">D41+E40</f>
-        <v>-4665092.60267499</v>
+        <v>-4677811.14196545</v>
       </c>
       <c r="F41" s="6" t="n">
         <f aca="false">E41+F40</f>
-        <v>-5113794.03683119</v>
+        <v>-5130752.08921847</v>
       </c>
       <c r="G41" s="6" t="n">
         <f aca="false">F41+G40</f>
-        <v>-5485897.22471568</v>
+        <v>-5507094.79019979</v>
       </c>
       <c r="H41" s="6" t="n">
         <f aca="false">G41+H40</f>
-        <v>-5781651.32554825</v>
+        <v>-5807088.40412917</v>
       </c>
       <c r="I41" s="6" t="n">
         <f aca="false">H41+I40</f>
-        <v>-6001540.63352025</v>
+        <v>-6031217.22519799</v>
       </c>
       <c r="J41" s="6" t="n">
         <f aca="false">I41+J40</f>
-        <v>-6146386.02374932</v>
+        <v>-6180302.12852389</v>
       </c>
       <c r="K41" s="6" t="n">
         <f aca="false">J41+K40</f>
-        <v>-6217348.48590446</v>
+        <v>-6255504.10377584</v>
       </c>
       <c r="L41" s="6" t="n">
         <f aca="false">K41+L40</f>
-        <v>-6215876.85449622</v>
+        <v>-6258271.98546443</v>
       </c>
       <c r="M41" s="6" t="n">
         <f aca="false">L41+M40</f>
-        <v>-6143646.5001957</v>
+        <v>-6190281.14426073</v>
       </c>
       <c r="N41" s="6" t="n">
         <f aca="false">M41+N40</f>
-        <v>-6060095.63254859</v>
+        <v>-6060095.6325486</v>
       </c>
       <c r="O41" s="6" t="n">
         <f aca="false">N41+O40</f>
-        <v>-5865201.49497795</v>
+        <v>-5878540.25555778</v>
       </c>
       <c r="P41" s="6" t="n">
         <f aca="false">O41+P40</f>
-        <v>-5609619.35779619</v>
+        <v>-5636296.87895585</v>
       </c>
       <c r="Q41" s="6" t="n">
         <f aca="false">P41+Q40</f>
-        <v>-5293016.80202847</v>
+        <v>-5333033.08376795</v>
       </c>
       <c r="R41" s="6" t="n">
         <f aca="false">Q41+R40</f>
-        <v>-4914968.28419538</v>
+        <v>-4968323.32651469</v>
       </c>
       <c r="S41" s="6" t="n">
         <f aca="false">R41+S40</f>
-        <v>-4474996.91021556</v>
+        <v>-4541690.7131147</v>
       </c>
       <c r="T41" s="6" t="n">
         <f aca="false">S41+T40</f>
-        <v>-3972603.4749453</v>
+        <v>-4052636.03842427</v>
       </c>
       <c r="U41" s="6" t="n">
         <f aca="false">T41+U40</f>
-        <v>-3407287.09526693</v>
+        <v>-3500658.41932572</v>
       </c>
       <c r="V41" s="6" t="n">
         <f aca="false">U41+V40</f>
-        <v>-2778559.62886006</v>
+        <v>-2885269.71349868</v>
       </c>
       <c r="W41" s="6" t="n">
         <f aca="false">V41+W40</f>
-        <v>-2085955.49100083</v>
+        <v>-2206004.33621927</v>
       </c>
       <c r="X41" s="6" t="n">
         <f aca="false">W41+X40</f>
-        <v>-1329038.05834588</v>
+        <v>-1462425.66414415</v>
       </c>
       <c r="Y41" s="6" t="n">
         <f aca="false">X41+Y40</f>
-        <v>-507403.549534932</v>
+        <v>-654129.91591303</v>
       </c>
       <c r="Z41" s="6" t="n">
         <f aca="false">Y41+Z40</f>
-        <v>219251.817974591</v>
+        <v>219251.81797459</v>
       </c>
       <c r="AA41" s="6" t="n">
         <f aca="false">Z41+AA40</f>
-        <v>1087926.29952119</v>
+        <v>905853.668513477</v>
       </c>
       <c r="AB41" s="6" t="n">
         <f aca="false">AA41+AB40</f>
-        <v>2018738.28794841</v>
+        <v>1654593.02593299</v>
       </c>
       <c r="AC41" s="6" t="n">
         <f aca="false">AB41+AC40</f>
-        <v>3011937.18421048</v>
+        <v>2465719.29118735</v>
       </c>
       <c r="AD41" s="6" t="n">
         <f aca="false">AC41+AD40</f>
-        <v>4067741.05974113</v>
+        <v>3339450.53571029</v>
       </c>
       <c r="AE41" s="6" t="n">
         <f aca="false">AD41+AE40</f>
-        <v>5186338.19556322</v>
+        <v>4275975.04052468</v>
       </c>
       <c r="AF41" s="6" t="n">
         <f aca="false">AE41+AF40</f>
-        <v>6367888.74975586</v>
+        <v>5275452.96370961</v>
       </c>
       <c r="AG41" s="6" t="n">
         <f aca="false">AF41+AG40</f>
-        <v>7612526.46806667</v>
+        <v>6338018.05101271</v>
       </c>
       <c r="AH41" s="6" t="n">
         <f aca="false">AG41+AH40</f>
-        <v>8920360.37718462</v>
+        <v>7463779.32912295</v>
       </c>
       <c r="AI41" s="6" t="n">
         <f aca="false">AH41+AI40</f>
-        <v>10291476.4192195</v>
+        <v>8652822.74015009</v>
       </c>
       <c r="AJ41" s="6" t="n">
         <f aca="false">AI41+AJ40</f>
-        <v>11725939.0004432</v>
+        <v>9905212.69036611</v>
       </c>
       <c r="AK41" s="6" t="n">
         <f aca="false">AJ41+AK40</f>
-        <v>13223792.4382753</v>
+        <v>11220993.4971905</v>
       </c>
       <c r="AL41" s="6" t="n">
         <f aca="false">AK41+AL40</f>
